--- a/stories/arbres/ATOM-SAN.ALI.003-08.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Andrée joue dans le jardin. Le soleil chauffe. Andrée a soif. Sa bouche est sèche. Maman est près des tomates. Andrée dit : j'ai soif, maman. Maman sourit. Elles vont dans la cuisine. Maman prend un verre. Elle verse de l'eau. L'eau est claire. Andrée prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore. Maman dit : quand on a soif, on boit de l'eau. Dans un verre. Andrée pose le verre. Elle se sent mieux. Plus tard, au jardin, Andrée a encore soif. Elle va vers maman. Maman tend le verre d'eau. Andrée boit. La soif s'en va.</t>
+          <t>Andrée joue dans le jardin. Le soleil chauffe. Andrée a soif. Sa bouche est sèche. Maman est près des tomates. J'ai soif, maman. Maman sourit. Elles vont dans la cuisine. Maman prend un verre. Elle verse de l'eau. L'eau est claire. Andrée prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Andrée pose le verre. Elle se sent mieux. Plus tard, au jardin, Andrée a encore soif. Elle va vers maman. Maman tend le verre d'eau. Andrée boit. La soif s'en va.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Andrée joue dans le jardin. Le soleil chauffe. Andrée a soif. Sa bouche est sèche. Maman est près des tomates.
+enfant-f|J'ai soif, maman. Maman sourit. Elles vont dans la cuisine. Maman prend un verre. Elle verse de l'eau. L'eau est claire.
+narrateur|Andrée prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore.
+maman|Quand on a soif, on boit de l'eau.
+narrateur|Dans un verre. Andrée pose le verre. Elle se sent mieux. Plus tard, au jardin, Andrée a encore soif. Elle va vers maman. Maman tend le verre d'eau. Andrée boit. La soif s'en va.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Andrée a soif. Que prend-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Andrée avait soif. Elle a pris le verre. Elle a bu de l'eau. Maman était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Andrée retourne au jardin. Le verre reste sur la table. Merci, dit Andrée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-08.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Dans un verre. Andrée pose le verre. Elle se sent mieux. Plus tard, au jardin, Andrée a encore soif. Elle va vers maman. Maman tend le verre d'eau. Andrée boit. La soif s'en va.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Andrée a soif. Que prend-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Andrée avait soif. Elle a pris le verre. Elle a bu de l'eau. Maman était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Andrée retourne au jardin. Le verre reste sur la table. Merci, dit Andrée.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.003-08.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Andrée boit un verre d'eau</t>
+          <t>Les tomates et l'eau fraîche</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'arrosoir goutte. Les tomates sentent le soleil. Mila a soif. Elles vont à la cuisine. Mila boit dans un verre. Au jardin, elle reprend de l'eau.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Andrée joue dans le jardin. Le soleil chauffe. Andrée a soif. Sa bouche est sèche. Maman est près des tomates. J'ai soif, maman. Maman sourit. Elles vont dans la cuisine. Maman prend un verre. Elle verse de l'eau. L'eau est claire. Andrée prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Andrée pose le verre. Elle se sent mieux. Plus tard, au jardin, Andrée a encore soif. Elle va vers maman. Maman tend le verre d'eau. Andrée boit. La soif s'en va.</t>
+          <t>L'arrosoir goutte sur la terre. Ploc. Ploc. Ploc. Les tomates sentent le soleil. Elles sont rouges, tout rondes. Mila vit ici, avec maman. Papa est à la maison, tout près. La terre est tiède sous les pieds. Mila tient l'arrosoir. Il est un peu lourd. Doucement, Mila. Un peu d'eau pour les tomates. Une tomate brille. Elle est rouge, maman ! Oui. Comme une petite balle. Le soleil chauffe le dos. Mila a la bouche sèche. J'ai soif, maman. Tu as soif ? Viens. On va à la cuisine. Elles quittent le jardin. Le carrelage est frais. Ça fait du bien aux pieds. Viens t'asseoir. Mila va vers sa chaise. Elle s'assoit près de maman. Elle pose les pieds par terre. Bravo, Mila. Tu es bien assise. Maman prend un verre. Elle verse de l'eau. L'eau est claire. Tu prends le verre ? Mila prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Bravo, Mila. Mila pose le verre. Merci maman. Tu te sens mieux ? Oui. Plus tard, au jardin, Mila a encore soif. Maman, j'ai encore soif. Voici le verre d'eau. Maman tend le verre. Mila boit. Bravo. La soif s'en va.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1329,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Andrée joue dans le jardin. Le soleil chauffe. Andrée a soif. Sa bouche est sèche. Maman est près des tomates.
-enfant-f|J'ai soif, maman. Maman sourit. Elles vont dans la cuisine. Maman prend un verre. Elle verse de l'eau. L'eau est claire.
-narrateur|Andrée prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore.
+          <t>narrateur|L'arrosoir goutte sur la terre.
+narrateur|Ploc. Ploc. Ploc.
+narrateur|Les tomates sentent le soleil.
+narrateur|Elles sont rouges, tout rondes.
+narrateur|Mila vit ici, avec maman.
+narrateur|Papa est à la maison, tout près.
+narrateur|La terre est tiède sous les pieds.
+narrateur|Mila tient l'arrosoir.
+narrateur|Il est un peu lourd.
+maman|Doucement, Mila.
+maman|Un peu d'eau pour les tomates.
+narrateur|Une tomate brille.
+enfant-f|Elle est rouge, maman !
+maman|Oui.
+maman|Comme une petite balle.
+narrateur|Le soleil chauffe le dos.
+narrateur|Mila a la bouche sèche.
+enfant-f|J'ai soif, maman.
+maman|Tu as soif ?
+maman|Viens.
+maman|On va à la cuisine.
+narrateur|Elles quittent le jardin.
+narrateur|Le carrelage est frais.
+narrateur|Ça fait du bien aux pieds.
+maman|Viens t'asseoir.
+narrateur|Mila va vers sa chaise.
+narrateur|Elle s'assoit près de maman.
+narrateur|Elle pose les pieds par terre.
+maman|Bravo, Mila.
+maman|Tu es bien assise.
+narrateur|Maman prend un verre.
+narrateur|Elle verse de l'eau.
+narrateur|L'eau est claire.
+maman|Tu prends le verre ?
+narrateur|Mila prend le verre d'eau.
+narrateur|Elle boit une gorgée.
+enfant-f|C'est frais.
+narrateur|Elle boit encore.
 maman|Quand on a soif, on boit de l'eau.
-narrateur|Dans un verre. Andrée pose le verre. Elle se sent mieux. Plus tard, au jardin, Andrée a encore soif. Elle va vers maman. Maman tend le verre d'eau. Andrée boit. La soif s'en va.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Dans un verre.
+maman|Bravo, Mila.
+narrateur|Mila pose le verre.
+enfant-f|Merci maman.
+maman|Tu te sens mieux ?
+enfant-f|Oui.
+narrateur|Plus tard, au jardin, Mila a encore soif.
+enfant-f|Maman, j'ai encore soif.
+maman|Voici le verre d'eau.
+narrateur|Maman tend le verre.
+narrateur|Mila boit.
+maman|Bravo.
+maman|La soif s'en va.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>arrosoir,verre</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1412,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Andrée a soif. Que prend-elle ?</t>
+          <t>Mila a soif. Que prend-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1572,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Andrée a soif. Que prend-elle ?</t>
+          <t>narrateur|Mila a soif.
+narrateur|Que prend-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1601,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Andrée avait soif. Elle a pris le verre. Elle a bu de l'eau. Maman était là.</t>
+          <t>Mila avait soif. Elle a pris le verre. Elle a bu de l'eau. Tu as pris le verre ? Oui, maman. J'ai bu de l'eau. Bravo, Mila. C'est du bon travail. Le verre reste près d'elle.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1745,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Andrée avait soif. Elle a pris le verre. Elle a bu de l'eau. Maman était là.</t>
+          <t>narrateur|Mila avait soif.
+narrateur|Elle a pris le verre.
+narrateur|Elle a bu de l'eau.
+maman|Tu as pris le verre ?
+enfant-f|Oui, maman.
+enfant-f|J'ai bu de l'eau.
+maman|Bravo, Mila.
+maman|C'est du bon travail.
+narrateur|Le verre reste près d'elle.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1781,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Andrée retourne au jardin. Le verre reste sur la table. Merci, dit Andrée.</t>
+          <t>Mila retourne au jardin. Le verre reste sur la table. L'arrosoir attend près des tomates. Merci, maman. Merci, Mila. Les tomates ont de l'eau. Et toi aussi. Moi, dans un verre. Oui. Quand on a soif, on boit de l'eau. On reste encore un peu ? Oui. Une tomate brille encore. Tu as fait du bon travail. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1921,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Andrée retourne au jardin. Le verre reste sur la table. Merci, dit Andrée.</t>
+          <t>narrateur|Mila retourne au jardin.
+narrateur|Le verre reste sur la table.
+narrateur|L'arrosoir attend près des tomates.
+enfant-f|Merci, maman.
+maman|Merci, Mila.
+maman|Les tomates ont de l'eau.
+maman|Et toi aussi.
+enfant-f|Moi, dans un verre.
+maman|Oui.
+maman|Quand on a soif, on boit de l'eau.
+maman|On reste encore un peu ?
+enfant-f|Oui.
+narrateur|Une tomate brille encore.
+maman|Tu as fait du bon travail.
+maman|Bravo.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'avais soif. J'ai pris le verre. J'ai bu de l'eau. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2103,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'avais soif.
+enfant-f|J'ai pris le verre.
+enfant-f|J'ai bu de l'eau.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2168,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-08.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-08.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'arrosoir goutte sur la terre. Ploc. Ploc. Ploc. Les tomates sentent le soleil. Elles sont rouges, tout rondes. Mila vit ici, avec maman. Papa est à la maison, tout près. La terre est tiède sous les pieds. Mila tient l'arrosoir. Il est un peu lourd. Doucement, Mila. Un peu d'eau pour les tomates. Une tomate brille. Elle est rouge, maman ! Oui. Comme une petite balle. Le soleil chauffe le dos. Mila a la bouche sèche. J'ai soif, maman. Tu as soif ? Viens. On va à la cuisine. Elles quittent le jardin. Le carrelage est frais. Ça fait du bien aux pieds. Viens t'asseoir. Mila va vers sa chaise. Elle s'assoit près de maman. Elle pose les pieds par terre. Bravo, Mila. Tu es bien assise. Maman prend un verre. Elle verse de l'eau. L'eau est claire. Tu prends le verre ? Mila prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Bravo, Mila. Mila pose le verre. Merci maman. Tu te sens mieux ? Oui. Plus tard, au jardin, Mila a encore soif. Maman, j'ai encore soif. Voici le verre d'eau. Maman tend le verre. Mila boit. Bravo. La soif s'en va.</t>
+          <t>L'arrosoir goutte sur la terre. Ploc. Ploc. Ploc. Les tomates sentent le soleil. Elles sont rouges, tout rondes. Mila vit ici, avec maman. Papa est à la maison, tout près. La terre est tiède sous les pieds. Mila tient l'arrosoir. L'anse est tiède. Il est un peu lourd. Doucement, Mila. Un peu d'eau pour les tomates. Une tomate brille. Une coccinelle marche dessus. Elle est rouge, maman ! Oui. La tomate, ou la coccinelle ? Les deux ! Comme de petites balles. Le soleil chauffe le dos. Mila a la bouche sèche. J'ai soif, maman. Tu as soif ? Viens. On va à la cuisine. Elles quittent le jardin. Le carrelage est frais. Ça fait du bien aux pieds. Ça sent encore le jardin. Tu as les pieds tout chauds, hein ? Oui. Et la bouche sèche. Viens t'asseoir. Mila va vers sa chaise. Elle s'assoit près de maman. Elle pose les pieds par terre. Bravo, Mila. Tu es bien assise. Maman prend un verre. Elle verse de l'eau. L'eau est claire. Tu prends le verre ? Mila prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Bravo, Mila. Mila pose le verre. Merci maman. Tu te sens mieux ? Oui. Plus tard, au jardin, Mila a encore soif. Maman, j'ai encore soif. Voici le verre d'eau. Maman tend le verre. Mila boit. Bravo. La soif s'en va.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Andrée joue dans le jardin. Le soleil chauffe. Andrée a soif. Sa bouche est sèche. Maman est près des tomates. Andrée dit : j'ai soif, maman. Maman sourit. Elles vont dans la cuisine. Maman prend un verre. Elle verse de l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. L'eau est claire. Andrée prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore. Maman dit : quand on a soif, on boit de l'eau. Dans un verre. Andrée pose le verre. Elle se sent mieux. Plus tard, au jardin, Andrée a encore soif. Elle va vers maman. Maman tend le verre d'eau. Andrée boit. La soif s'en va.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'arrosoir goutte sur la terre. Ploc. Ploc. Ploc. Les tomates sentent le soleil. Elles sont rouges, tout rondes. Mila vit ici, avec maman. Papa est à la maison, tout près. La terre est tiède sous les pieds. Mila tient l'arrosoir. L'anse est tiède. Il est un peu lourd. Doucement, Mila. Un peu d'eau pour les tomates. Une tomate brille. Une coccinelle marche dessus. Elle est rouge, maman ! Oui. La tomate, ou la coccinelle ? Les deux ! Comme de petites balles. Le soleil chauffe le dos. Mila a la bouche sèche. J'ai soif, maman. Tu as soif ? Viens. On va à la cuisine. Elles quittent le jardin. Le carrelage est frais. Ça fait du bien aux pieds. Ça sent encore le jardin. Tu as les pieds tout chauds, hein ? Oui. Et la bouche sèche. Viens t'asseoir. Mila va vers sa chaise. Elle s'assoit près de maman. Elle pose les pieds par terre. Bravo, Mila. Tu es bien assise. Maman prend un verre. Elle verse de l'eau. L'eau est claire. Tu prends le verre ? Mila prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Bravo, Mila. Mila pose le verre. Merci maman. Tu te sens mieux ? Oui. Plus tard, au jardin, Mila a encore soif. Maman, j'ai encore soif. Voici le verre d'eau. Maman tend le verre. Mila boit. Bravo. La soif s'en va.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1337,13 +1337,17 @@
 narrateur|Papa est à la maison, tout près.
 narrateur|La terre est tiède sous les pieds.
 narrateur|Mila tient l'arrosoir.
+narrateur|L'anse est tiède.
 narrateur|Il est un peu lourd.
 maman|Doucement, Mila.
 maman|Un peu d'eau pour les tomates.
 narrateur|Une tomate brille.
+narrateur|Une coccinelle marche dessus.
 enfant-f|Elle est rouge, maman !
 maman|Oui.
-maman|Comme une petite balle.
+maman|La tomate, ou la coccinelle ?
+enfant-f|Les deux !
+maman|Comme de petites balles.
 narrateur|Le soleil chauffe le dos.
 narrateur|Mila a la bouche sèche.
 enfant-f|J'ai soif, maman.
@@ -1353,6 +1357,10 @@
 narrateur|Elles quittent le jardin.
 narrateur|Le carrelage est frais.
 narrateur|Ça fait du bien aux pieds.
+narrateur|Ça sent encore le jardin.
+maman|Tu as les pieds tout chauds, hein ?
+enfant-f|Oui.
+enfant-f|Et la bouche sèche.
 maman|Viens t'asseoir.
 narrateur|Mila va vers sa chaise.
 narrateur|Elle s'assoit près de maman.
@@ -1417,7 +1425,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Andrée a &lt;emphasis level="moderate"&gt;soif&lt;/emphasis&gt;. Que prend-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a soif. Que prend-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1576,7 +1584,6 @@
 narrateur|Que prend-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1601,12 +1608,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila avait soif. Elle a pris le verre. Elle a bu de l'eau. Tu as pris le verre ? Oui, maman. J'ai bu de l'eau. Bravo, Mila. C'est du bon travail. Le verre reste près d'elle.</t>
+          <t>Mila avait soif. Elle a pris le verre. Elle a bu de l'eau. Tu as pris le verre ? Oui, maman. J'ai bu de l'eau. Bravo, Mila. Le verre reste près d'elle.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Andrée avait soif. Elle a pris le verre. Elle a bu de l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. Maman était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila avait soif. Elle a pris le verre. Elle a bu de l'eau. Tu as pris le verre ? Oui, maman. J'ai bu de l'eau. Bravo, Mila. Le verre reste près d'elle.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1752,11 +1759,9 @@
 enfant-f|Oui, maman.
 enfant-f|J'ai bu de l'eau.
 maman|Bravo, Mila.
-maman|C'est du bon travail.
 narrateur|Le verre reste près d'elle.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1781,12 +1786,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mila retourne au jardin. Le verre reste sur la table. L'arrosoir attend près des tomates. Merci, maman. Merci, Mila. Les tomates ont de l'eau. Et toi aussi. Moi, dans un verre. Oui. Quand on a soif, on boit de l'eau. On reste encore un peu ? Oui. Une tomate brille encore. Tu as fait du bon travail. Bravo.</t>
+          <t>Mila retourne au jardin. Le verre reste sur la table. L'arrosoir attend près des tomates. Merci, maman. Merci, Mila. Les tomates ont de l'eau. Et toi aussi. Moi, dans un verre. Oui. Quand on a soif, on boit de l'eau. On reste encore un peu ? Oui. Une tomate brille encore. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Andrée retourne au jardin. Le &lt;emphasis level="moderate"&gt;verre&lt;/emphasis&gt; reste sur la table. Merci, dit Andrée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila retourne au jardin. Le verre reste sur la table. L'arrosoir attend près des tomates. Merci, maman. Merci, Mila. Les tomates ont de l'eau. Et toi aussi. Moi, dans un verre. Oui. Quand on a soif, on boit de l'eau. On reste encore un peu ? Oui. Une tomate brille encore. Bravo.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1934,11 +1939,9 @@
 maman|On reste encore un peu ?
 enfant-f|Oui.
 narrateur|Une tomate brille encore.
-maman|Tu as fait du bon travail.
 maman|Bravo.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1963,12 +1966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'avais soif. J'ai pris le verre. J'ai bu de l'eau. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>J'avais soif. J'ai pris le verre. J'ai bu de l'eau. Bravo.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'avais soif. J'ai pris le verre. J'ai bu de l'eau. Bravo.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2106,12 +2109,9 @@
           <t>enfant-f|J'avais soif.
 enfant-f|J'ai pris le verre.
 enfant-f|J'ai bu de l'eau.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2130,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2175,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-08.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-08.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Andrée, maman</t>
+          <t>Mila, maman</t>
         </is>
       </c>
     </row>
